--- a/artfynd/A 54297-2022 artfynd.xlsx
+++ b/artfynd/A 54297-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54297-2022 artfynd.xlsx
+++ b/artfynd/A 54297-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74294366</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384631.9146075149</v>
+        <v>384632</v>
       </c>
       <c r="R2" t="n">
-        <v>6680925.701303929</v>
+        <v>6680926</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +753,9 @@
           <t>2018-10-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,7 +795,7 @@
         <v>74294369</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -847,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384542.9601562964</v>
+        <v>384543</v>
       </c>
       <c r="R3" t="n">
-        <v>6680929.506591789</v>
+        <v>6680930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,19 +870,9 @@
           <t>2018-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1059,7 +1039,7 @@
         <v>74294363</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384778.6452057984</v>
+        <v>384779</v>
       </c>
       <c r="R5" t="n">
-        <v>6680860.458220189</v>
+        <v>6680860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,19 +1114,9 @@
           <t>2018-10-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54297-2022 artfynd.xlsx
+++ b/artfynd/A 54297-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74294366</v>
+        <v>74294364</v>
       </c>
       <c r="B2" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Översjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384632</v>
+        <v>384701</v>
       </c>
       <c r="R2" t="n">
-        <v>6680926</v>
+        <v>6680847</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,58 +782,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74294369</v>
+        <v>88757127</v>
       </c>
       <c r="B3" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Översjöberget, Vrm</t>
+          <t>Ötjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384543</v>
+        <v>383744</v>
       </c>
       <c r="R3" t="n">
-        <v>6680930</v>
+        <v>6680963</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-06</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-06</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,43 +864,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74294368</v>
+        <v>88757129</v>
       </c>
       <c r="B4" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,42 +894,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Översjöberget, Vrm</t>
+          <t>Ötjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384542.9601562964</v>
+        <v>383744</v>
       </c>
       <c r="R4" t="n">
-        <v>6680929.506591789</v>
+        <v>6680963</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-10-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,43 +965,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74294363</v>
+        <v>88757130</v>
       </c>
       <c r="B5" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,42 +995,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Översjöberget, Vrm</t>
+          <t>Ötjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384779</v>
+        <v>383744</v>
       </c>
       <c r="R5" t="n">
-        <v>6680860</v>
+        <v>6680963</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,12 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-10-06</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-10-06</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,28 +1066,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1156,12 +1088,7 @@
         <v>74294367</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384603.7822358672</v>
+        <v>384604</v>
       </c>
       <c r="R6" t="n">
-        <v>6680933.048672324</v>
+        <v>6680933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,19 +1158,9 @@
           <t>2018-10-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-10-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,15 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74294364</v>
+        <v>74294362</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,34 +1208,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Översjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>384700.5747785638</v>
+        <v>384779</v>
       </c>
       <c r="R7" t="n">
-        <v>6680846.527894532</v>
+        <v>6680860</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,19 +1270,14 @@
           <t>2018-10-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-10-06</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>larverna är omtyckta av hackspettar!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,7 +1296,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1405,12 +1317,7 @@
         <v>74294365</v>
       </c>
       <c r="B8" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384631.9146075149</v>
+        <v>384632</v>
       </c>
       <c r="R8" t="n">
-        <v>6680925.701303929</v>
+        <v>6680926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,19 +1387,9 @@
           <t>2018-10-06</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-10-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,15 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74294362</v>
+        <v>74294368</v>
       </c>
       <c r="B9" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384778.6452057984</v>
+        <v>384543</v>
       </c>
       <c r="R9" t="n">
-        <v>6680860.458220189</v>
+        <v>6680930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,24 +1499,9 @@
           <t>2018-10-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-10-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>larverna är omtyckta av hackspettar!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,6 +1535,342 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>74294363</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Översjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>384779</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6680860</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>74294366</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Översjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>384632</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6680926</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-10-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-10-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>74294369</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Översjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>384543</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6680930</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-10-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-10-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54297-2022 artfynd.xlsx
+++ b/artfynd/A 54297-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74294364</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88757127</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88757129</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88757130</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74294367</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74294362</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74294365</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74294368</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74294363</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74294366</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1871,8 +1926,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74294369</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>